--- a/BWI/bestwine_output/bestwine_Faroe Islands.xlsx
+++ b/BWI/bestwine_output/bestwine_Faroe Islands.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +43,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004F1A2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,8 +434,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AA5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -655,7 +664,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>rusan@rusan.fo</t>
@@ -671,16 +679,11 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/r-sdrekkas-la-landsins/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Áki Johannesen Dahl</t>
@@ -691,8 +694,6 @@
           <t>Sales Manager</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/%C3%A1ki-johannesen-dahl-a20935193/</t>
@@ -760,7 +761,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>rusan@rusan.fo</t>
@@ -776,16 +776,11 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/r-sdrekkas-la-landsins/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Rogvi Andrias Fossadal</t>
@@ -796,11 +791,203 @@
           <t>Ceo</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/fossadal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Rúsdrekkasøla Landsins</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Rúsdrekkasøla Landsins</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>29879</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Faroe Islands</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Thorshavn</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Streymoy</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14 Skálatrøð</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://rusan.fo</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>rusan@rusan.fo</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>+298 340400</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/r-sdrekkas-la-landsins/</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Oddbjørg Højgaard</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oddbj%C3%B8rg-h%C3%B8jgaard-5503a330/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Rúsdrekkasøla Landsins</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Rúsdrekkasøla Landsins</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>29879</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Faroe Islands</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Thorshavn</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Streymoy</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14 Skálatrøð</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://rusan.fo</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>rusan@rusan.fo</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>+298 340400</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/r-sdrekkas-la-landsins/</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Áki Johannesen</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%C3%A1ki-johannesen-dahl-a20935193/</t>
         </is>
       </c>
     </row>
